--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:33:50+00:00</t>
+    <t>2023-05-09T07:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:27:04+00:00</t>
+    <t>2023-05-09T07:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T12:40:41+00:00</t>
+    <t>2023-05-09T14:46:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -458,7 +458,7 @@
     <t>Autorité d'enregistrement représentant une institution (Ordre/ARS).</t>
   </si>
   <si>
-    <t>La civilité, le nom et le prénom sous lequels exerce le professionnel.</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour définir l'identité d’exercice d’un professionnel.</t>
   </si>
   <si>
     <t>Synonyme MOS : AutoriteEnregistrement</t>
@@ -474,13 +474,13 @@
 </t>
   </si>
   <si>
-    <t>InscriptionOrdre</t>
-  </si>
-  <si>
     <t>Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
-    <t>Synonymes RPPS : Inscription à ordre</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
+  </si>
+  <si>
+    <t>Synonymes RPPS : InscriptionOrdre</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-education-level</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-practitionerrole</t>
+    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T14:46:02+00:00</t>
+    <t>2023-05-12T07:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,7 +451,7 @@
     <t>as-ext-practitionerrole-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitionerrole-name}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
 </t>
   </si>
   <si>
@@ -461,7 +461,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour définir l'identité d’exercice d’un professionnel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : AutoriteEnregistrement</t>
+    <t>Synonyme : AutoriteEnregistrement, Ordre</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-registration</t>
@@ -470,7 +470,7 @@
     <t>as-ext-practitionerrole-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitionerrole-registration}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
 </t>
   </si>
   <si>
@@ -489,30 +489,30 @@
     <t>as-ext-practitionerrole-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitionerrole-education-level}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
 </t>
   </si>
   <si>
+    <t>Savoir-faire (qualifications/autres attributions).</t>
+  </si>
+  <si>
+    <t>Le niveau de formation.</t>
+  </si>
+  <si>
     <t>Synonyme MOS : SavoirFaire</t>
   </si>
   <si>
-    <t>Le niveau de formation.</t>
-  </si>
-  <si>
-    <t>Savoir-faire (qualifications/autres attributions).</t>
-  </si>
-  <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-smartcard</t>
   </si>
   <si>
     <t>as-ext-practitionerrole-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitionerrole-smartcard}
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
 </t>
   </si>
   <si>
-    <t>Synonyme MOS : Numéro de carte du professionnel.</t>
+    <t>Numéro de carte du professionnel.</t>
   </si>
   <si>
     <t>Données descriptives du moyen d’identification des personnes physiques via une carte de professionnel.</t>
@@ -544,13 +544,13 @@
 </t>
   </si>
   <si>
+    <t>identifiant métier calculé à partir des identifiants techniques de l'exercice professionnel et la situation d'exercice.</t>
+  </si>
+  <si>
+    <t>Business Identifiers that are specific to a role/location.</t>
+  </si>
+  <si>
     <t>Synonyme MOS : idFonctionnel</t>
-  </si>
-  <si>
-    <t>Business Identifiers that are specific to a role/location.</t>
-  </si>
-  <si>
-    <t>identifiant métier calculé à partir des identifiants techniques de l'exercice professionnel et la situation d'exercice.</t>
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
@@ -664,13 +664,13 @@
     <t>PractitionerRole.identifier.value</t>
   </si>
   <si>
-    <t>Synonyme MOS : idActivite</t>
+    <t>Identifiant technique de l'activité.</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>Identifiant technique de l'activité.</t>
+    <t>Synonyme : idActivite</t>
   </si>
   <si>
     <t>123456</t>
@@ -733,7 +733,7 @@
 </t>
   </si>
   <si>
-    <t>la sitation d'exercice est-elle active? active/inactive</t>
+    <t>La sitation d'exercice est-elle active? (active | inactive)</t>
   </si>
   <si>
     <t>Whether this practitioner role record is in active use.</t>
@@ -798,7 +798,7 @@
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateFinActivite</t>
+    <t>Synonyme : dateFinActivite</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
@@ -820,7 +820,7 @@
     <t>Practitioner that is able to provide the defined services for the organization.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idPP</t>
+    <t>Synonyme : idPP</t>
   </si>
   <si>
     <t>PractitionerRole.organization</t>
@@ -836,7 +836,7 @@
     <t>The organization where the Practitioner performs the roles associated.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idStructure</t>
+    <t>Synonyme : idNat_Strcut</t>
   </si>
   <si>
     <t>PractitionerRole.code</t>
@@ -901,7 +901,7 @@
     <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant.</t>
   </si>
   <si>
-    <t>Synonyme MOS : categorieProfessionnelle</t>
+    <t>Synonyme : categorieProfessionnelle</t>
   </si>
   <si>
     <t>Liste des catégories professionnelles</t>
@@ -919,7 +919,7 @@
     <t>Profession exercée ou future profession de l'étudiant.</t>
   </si>
   <si>
-    <t>Synonyme MOS : professionSante</t>
+    <t>Synonyme : professionSante</t>
   </si>
   <si>
     <t>Liste des professions de santé  définies par le code de la santé publique</t>
@@ -937,7 +937,7 @@
     <t>Profession du social.</t>
   </si>
   <si>
-    <t>Synonyme MOS : professionSocial</t>
+    <t>Synonyme : professionSocial</t>
   </si>
   <si>
     <t>Liste des professions du social</t>
@@ -952,7 +952,7 @@
     <t>Profession à usage de titre professionnel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : usagerTitre</t>
+    <t>Synonyme : usagerTitre</t>
   </si>
   <si>
     <t>Liste des professions à usage de titre professionnel</t>
@@ -967,7 +967,7 @@
     <t>professionnel non membre d'une profession réglementée.</t>
   </si>
   <si>
-    <t>Synonyme MOS : autreProfession</t>
+    <t>Synonyme : autreProfession</t>
   </si>
   <si>
     <t>Liste de professionnels non membres d'une profession réglementée</t>
@@ -982,7 +982,7 @@
     <t>Le genre identifiant une activité qui nécessite l’application de règles de gestion spécifiques.</t>
   </si>
   <si>
-    <t>Synonyme MOS : genreActivite</t>
+    <t>Synonyme : genreActivite</t>
   </si>
   <si>
     <t>Liste des genres d'activité</t>
@@ -1000,7 +1000,7 @@
     <t>Le mode d'exercice décrit selon quelle modalité une activité est exercée au regard de l'organisation de la rétribution du professionnel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : modeExercice</t>
+    <t>Synonyme : modeExercice</t>
   </si>
   <si>
     <t>Liste des modes d'exercice</t>
@@ -1015,10 +1015,13 @@
     <t>typeActiviteLiberale</t>
   </si>
   <si>
-    <t>Synonyme MOS : typeActiviteLiberale</t>
-  </si>
-  <si>
-    <t>Type d’activité libérale, par exemple: Cabinet; Secteur privé à l'hôpital</t>
+    <t>Type d’activité libérale, par exemple: Cabinet; Secteur privé à l'hôpital.</t>
+  </si>
+  <si>
+    <t>Synonyme : typeActiviteLiberale</t>
+  </si>
+  <si>
+    <t>Liste des types d’activité</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J96-TypeActiviteLiberale-RASS/FHIR/JDV-J96-TypeActiviteLiberale-RASS</t>
@@ -1033,7 +1036,7 @@
     <t>Statut du professionnel du Service de santé des armées.</t>
   </si>
   <si>
-    <t>Synonyme MOS : statutProfessionnelSSA</t>
+    <t>Synonyme : statutProfessionnelSSA</t>
   </si>
   <si>
     <t>Liste des statuts SSA</t>
@@ -1051,7 +1054,7 @@
     <t>Statut hospitalier dans le cas d’une activité exercée en établissement public de santé.</t>
   </si>
   <si>
-    <t>Synonyme MOS : statutHospitalier</t>
+    <t>Synonyme : statutHospitalier</t>
   </si>
   <si>
     <t>Liste des statuts hospitaliers</t>
@@ -1069,7 +1072,7 @@
     <t>Fonction du professionnel au sein de la structure d’exercice.</t>
   </si>
   <si>
-    <t>Synonyme MOS : role</t>
+    <t>Synonyme : role</t>
   </si>
   <si>
     <t>Liste des fonctions et rôles</t>
@@ -1108,7 +1111,7 @@
     <t>Section du tableau de l’Ordre des pharmaciens (CNOP).</t>
   </si>
   <si>
-    <t>Synonyme MOS : sectionOrdrePharmacien</t>
+    <t>Synonyme : sectionOrdrePharmacien</t>
   </si>
   <si>
     <t>Liste des sections du tableau CNOP</t>
@@ -1126,7 +1129,7 @@
     <t>Sous-section ou à défaut section du tableau de l’Ordre des pharmaciens (CNOP).</t>
   </si>
   <si>
-    <t>Synonyme MOS : sousSectionOrdrePharmacien</t>
+    <t>Synonyme : sousSectionOrdrePharmacien</t>
   </si>
   <si>
     <t>Liste des sous-sections du tableau CNOP</t>
@@ -1153,7 +1156,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-codeableconcept-timed}
+    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
 </t>
   </si>
   <si>
@@ -1191,7 +1194,7 @@
     <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation.</t>
   </si>
   <si>
-    <t>Synonyme MOS : attributionParticuliere</t>
+    <t>Synonyme : attributionParticuliere</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J90-AttributionParticuliere-RASS/FHIR/JDV-J90-AttributionParticuliere-RASS</t>
@@ -1206,7 +1209,7 @@
     <t>Spécialité ordinale  reconnue par une autorité d'enregistrement (Ordre ou SSA).</t>
   </si>
   <si>
-    <t>Synonyme MOS : specialite</t>
+    <t>Synonyme : specialite</t>
   </si>
   <si>
     <t>Liste des spécialités ordinales</t>
@@ -1224,7 +1227,7 @@
     <t>Compétence acquise par le professionnel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : competence</t>
+    <t>Synonyme : competence</t>
   </si>
   <si>
     <t>Liste des compétences</t>
@@ -1239,7 +1242,7 @@
     <t>Compétence exclusive exercée par le professionnel à titre exclusif.</t>
   </si>
   <si>
-    <t>Synonyme MOS : competenceExclusive</t>
+    <t>Synonyme : competenceExclusive</t>
   </si>
   <si>
     <t>Liste des compétences exclusives</t>
@@ -1254,7 +1257,7 @@
     <t>Diplôme d'études spécialisées complémentaires (DESC).</t>
   </si>
   <si>
-    <t>Synonyme MOS : DESCnonQualifian</t>
+    <t>Synonyme : DESCnonQualifian</t>
   </si>
   <si>
     <t>Liste des DESC</t>
@@ -1269,7 +1272,7 @@
     <t>Capacité (savoir-faire)d e médecine</t>
   </si>
   <si>
-    <t>Synonyme MOS : capaciteSavoirFaire</t>
+    <t>Synonyme : capaciteSavoirFaire</t>
   </si>
   <si>
     <t>Liste des capacités</t>
@@ -1284,7 +1287,7 @@
     <t>Qualification de praticien adjoint contractuel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : qualificationPAC</t>
+    <t>Synonyme : qualificationPAC</t>
   </si>
   <si>
     <t>Liste des qualifications</t>
@@ -1299,7 +1302,7 @@
     <t>Fonction qualifiée.</t>
   </si>
   <si>
-    <t>Synonyme MOS : fonctionQualifiee</t>
+    <t>Synonyme : fonctionQualifiee</t>
   </si>
   <si>
     <t>Liste des fonctions qualifiées</t>
@@ -1314,7 +1317,7 @@
     <t>Droit d'exercice complémentaire.</t>
   </si>
   <si>
-    <t>Synonyme MOS : droitExerciceComplementaire</t>
+    <t>Synonyme : droitExerciceComplementaire</t>
   </si>
   <si>
     <t>Liste des droits d'exercice complémentaires</t>
@@ -1329,7 +1332,7 @@
     <t>Orientation particulière.</t>
   </si>
   <si>
-    <t>Synonyme MOS : orientationParticuliere</t>
+    <t>Synonyme : orientationParticuliere</t>
   </si>
   <si>
     <t>Liste des orientations particulières</t>
@@ -1344,7 +1347,7 @@
     <t>Le type de savoir-faire (qualifications/autres attributions).</t>
   </si>
   <si>
-    <t>Synonyme MOS : typeSavoirFaire</t>
+    <t>Synonyme : typeSavoirFaire</t>
   </si>
   <si>
     <t>Liste des types de savoir-faire</t>
@@ -1415,14 +1418,14 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>
     <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice.</t>
   </si>
   <si>
-    <t>Synonyme MOS : BoiteLettreMSS</t>
+    <t>Synonyme : BoiteLettreMSS</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -1898,7 +1901,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="123.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.7265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -6406,7 +6409,7 @@
         <v>274</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>276</v>
@@ -6437,10 +6440,10 @@
         <v>185</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>71</v>
@@ -6475,13 +6478,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>71</v>
@@ -6506,13 +6509,13 @@
         <v>272</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>276</v>
@@ -6543,10 +6546,10 @@
         <v>185</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -6581,13 +6584,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>71</v>
@@ -6612,13 +6615,13 @@
         <v>272</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>276</v>
@@ -6649,10 +6652,10 @@
         <v>185</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>71</v>
@@ -6687,13 +6690,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>71</v>
@@ -6718,13 +6721,13 @@
         <v>272</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>276</v>
@@ -6755,10 +6758,10 @@
         <v>185</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>71</v>
@@ -6793,13 +6796,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>71</v>
@@ -6824,13 +6827,13 @@
         <v>272</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>276</v>
@@ -6861,10 +6864,10 @@
         <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -6899,13 +6902,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>71</v>
@@ -6930,13 +6933,13 @@
         <v>272</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>276</v>
@@ -6967,10 +6970,10 @@
         <v>185</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>71</v>
@@ -7005,13 +7008,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>71</v>
@@ -7036,13 +7039,13 @@
         <v>272</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>276</v>
@@ -7073,10 +7076,10 @@
         <v>185</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>71</v>
@@ -7111,13 +7114,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>271</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>71</v>
@@ -7142,13 +7145,13 @@
         <v>272</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
         <v>274</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>276</v>
@@ -7179,10 +7182,10 @@
         <v>185</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>71</v>
@@ -7217,10 +7220,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7246,16 +7249,16 @@
         <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>71</v>
@@ -7304,7 +7307,7 @@
         <v>71</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>72</v>
@@ -7321,10 +7324,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7347,16 +7350,16 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7385,19 +7388,19 @@
         <v>185</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>71</v>
@@ -7406,7 +7409,7 @@
         <v>129</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>72</v>
@@ -7423,13 +7426,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>71</v>
@@ -7454,13 +7457,13 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7490,7 +7493,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>71</v>
@@ -7508,7 +7511,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7525,13 +7528,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>71</v>
@@ -7556,13 +7559,13 @@
         <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7591,10 +7594,10 @@
         <v>185</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>71</v>
@@ -7612,7 +7615,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7629,13 +7632,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -7660,13 +7663,13 @@
         <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7695,10 +7698,10 @@
         <v>185</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>71</v>
@@ -7716,7 +7719,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -7733,13 +7736,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>71</v>
@@ -7764,13 +7767,13 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7799,10 +7802,10 @@
         <v>185</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>71</v>
@@ -7820,7 +7823,7 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
@@ -7837,13 +7840,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>71</v>
@@ -7868,13 +7871,13 @@
         <v>190</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7903,10 +7906,10 @@
         <v>185</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>71</v>
@@ -7924,7 +7927,7 @@
         <v>71</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -7941,13 +7944,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>71</v>
@@ -7972,13 +7975,13 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8007,10 +8010,10 @@
         <v>185</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>71</v>
@@ -8028,7 +8031,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8045,13 +8048,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8076,13 +8079,13 @@
         <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8111,10 +8114,10 @@
         <v>185</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8132,7 +8135,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8149,13 +8152,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>71</v>
@@ -8180,13 +8183,13 @@
         <v>190</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8215,10 +8218,10 @@
         <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>71</v>
@@ -8236,7 +8239,7 @@
         <v>71</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>72</v>
@@ -8253,13 +8256,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>71</v>
@@ -8284,13 +8287,13 @@
         <v>190</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8319,10 +8322,10 @@
         <v>185</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>71</v>
@@ -8340,7 +8343,7 @@
         <v>71</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>72</v>
@@ -8357,13 +8360,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>71</v>
@@ -8388,13 +8391,13 @@
         <v>190</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8423,10 +8426,10 @@
         <v>185</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>71</v>
@@ -8444,7 +8447,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8461,13 +8464,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>71</v>
@@ -8492,13 +8495,13 @@
         <v>190</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8527,10 +8530,10 @@
         <v>185</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>71</v>
@@ -8548,7 +8551,7 @@
         <v>71</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>72</v>
@@ -8565,10 +8568,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8591,16 +8594,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8650,7 +8653,7 @@
         <v>71</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>72</v>
@@ -8667,10 +8670,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8693,16 +8696,16 @@
         <v>71</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8752,7 +8755,7 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
@@ -8769,10 +8772,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8795,17 +8798,17 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>71</v>
@@ -8842,7 +8845,7 @@
         <v>71</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
@@ -8852,7 +8855,7 @@
         <v>129</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -8864,18 +8867,18 @@
         <v>90</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>71</v>
@@ -8897,19 +8900,19 @@
         <v>71</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>71</v>
@@ -8958,7 +8961,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -8970,15 +8973,15 @@
         <v>90</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9001,16 +9004,16 @@
         <v>71</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9060,7 +9063,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9077,10 +9080,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9177,10 +9180,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9279,14 +9282,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9308,10 +9311,10 @@
         <v>123</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>126</v>
@@ -9366,7 +9369,7 @@
         <v>71</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9383,10 +9386,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9412,13 +9415,13 @@
         <v>99</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9447,10 +9450,10 @@
         <v>185</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>71</v>
@@ -9468,7 +9471,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9485,10 +9488,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9514,10 +9517,10 @@
         <v>227</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9568,7 +9571,7 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
@@ -9585,10 +9588,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9611,16 +9614,16 @@
         <v>71</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9670,7 +9673,7 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
@@ -9687,10 +9690,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9713,16 +9716,16 @@
         <v>71</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9772,7 +9775,7 @@
         <v>71</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
@@ -9789,10 +9792,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9815,13 +9818,13 @@
         <v>71</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9872,7 +9875,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -9889,10 +9892,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9989,10 +9992,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10091,14 +10094,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10120,10 +10123,10 @@
         <v>123</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>126</v>
@@ -10178,7 +10181,7 @@
         <v>71</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>72</v>
@@ -10195,10 +10198,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10224,13 +10227,13 @@
         <v>173</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10280,7 +10283,7 @@
         <v>71</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10297,10 +10300,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10326,10 +10329,10 @@
         <v>213</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>216</v>
@@ -10382,7 +10385,7 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
@@ -10399,10 +10402,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10428,13 +10431,13 @@
         <v>173</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10484,7 +10487,7 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
@@ -10501,10 +10504,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10527,19 +10530,19 @@
         <v>71</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>71</v>
@@ -10588,7 +10591,7 @@
         <v>71</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:42:29+00:00</t>
+    <t>2023-05-16T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,13 +455,13 @@
 </t>
   </si>
   <si>
-    <t>Autorité d'enregistrement représentant une institution (Ordre/ARS).</t>
+    <t>civiliteExercie + nomExercice + prenomExercice (ExerciceProfessionnel)</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour définir l'identité d’exercice d’un professionnel.</t>
   </si>
   <si>
-    <t>Synonyme : AutoriteEnregistrement, Ordre</t>
+    <t>Concaténation des champs MOS : civilite + nomExercice + prenom</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-registration</t>
@@ -474,13 +474,13 @@
 </t>
   </si>
   <si>
-    <t>Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
+    <t>Autorité d'enregistrement représentant une institution (Ordre/ARS).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
   </si>
   <si>
-    <t>Synonymes RPPS : InscriptionOrdre</t>
+    <t>Synonyme : AutoriteEnregistrement, Ordre</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-education-level</t>
@@ -1359,7 +1359,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrLocation) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrLocation)
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.3</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-16T12:00:29+00:00</t>
+    <t>2023-05-17T08:16:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASPractitionerRoleProfile</t>
+    <t>AsPractitionerRoleProfile</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:16:04+00:00</t>
+    <t>2023-05-26T10:09:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource PractitionerRole dans le contexte de l'Annuaire Santé pour décrire l'exercice professionel et la situation d'exercice | contient les informations décrivant notamment la profession exercée, l'identité d'exercice d'un professionnel, le cadre de son exercice (civil, militaire, etc.) ainsi que les caractéristiques de l'exercice d’un professionnel pendant une période déterminée et dans une structure déterminée.</t>
+    <t>Profil créé à partir de FrPractitionerRoleExercice dans le contexte de l'Annuaire Santé pour décrire l'exercice professionel et la situation d'exercice | contient les informations décrivant notamment la profession exercée, l'identité d'exercice d'un professionnel, le cadre de son exercice (civil, militaire, etc.) ainsi que les caractéristiques de l'exercice d’un professionnel pendant une période déterminée et dans une structure déterminée.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -455,7 +455,7 @@
 </t>
   </si>
   <si>
-    <t>civiliteExercie + nomExercice + prenomExercice (ExerciceProfessionnel)</t>
+    <t>La civilité, le nom et le prénom sous lequels exerce le professionnel.</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour définir l'identité d’exercice d’un professionnel.</t>
@@ -474,13 +474,13 @@
 </t>
   </si>
   <si>
-    <t>Autorité d'enregistrement représentant une institution (Ordre/ARS).</t>
+    <t>Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
   </si>
   <si>
-    <t>Synonyme : AutoriteEnregistrement, Ordre</t>
+    <t>Synonymes : InscriptionOrdre</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-education-level</t>
@@ -493,13 +493,10 @@
 </t>
   </si>
   <si>
-    <t>Savoir-faire (qualifications/autres attributions).</t>
+    <t>niveauFormation</t>
   </si>
   <si>
     <t>Le niveau de formation.</t>
-  </si>
-  <si>
-    <t>Synonyme MOS : SavoirFaire</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-smartcard</t>
@@ -512,13 +509,106 @@
 </t>
   </si>
   <si>
-    <t>Numéro de carte du professionnel.</t>
-  </si>
-  <si>
     <t>Données descriptives du moyen d’identification des personnes physiques via une carte de professionnel.</t>
   </si>
   <si>
-    <t>Synonyme MOS : CarteProfessionnel</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les informations de la carte CPx utilisée comme moyen d’identification des personnes physiques.</t>
+  </si>
+  <si>
+    <t>Synonyme : CarteProfessionnel 
+ La carte est rattachée à l’exercice d’une profession donnée et non au professionnel lui-même, un professionnel exerçant simultanément deux professions a deux cartes</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-digital-certificate</t>
+  </si>
+  <si>
+    <t>as-ext-digital-certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
+</t>
+  </si>
+  <si>
+    <t>AS Digital Certificate Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les certificats utilisés par les professionnels et les structures comme moyen d'identification.</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-end-cause</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-end-cause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
+</t>
+  </si>
+  <si>
+    <t>Motif de fin d'activité, par exemple: décès, retraite libérale, changement de profession, etc.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le motif de fin d'activité du professionnel (décès, retraite libérale, changement de profession par exemple.</t>
+  </si>
+  <si>
+    <t>Synonyme : motifFinActivite</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-contracted</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-contracted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
+</t>
+  </si>
+  <si>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+  </si>
+  <si>
+    <t>Synonyme : secteurConventionnement</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-hascas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
+</t>
+  </si>
+  <si>
+    <t>OPTAM est un dispositif proposé par l’Assurance Maladie aux médecins conventionnés, ayant pour objectif principal de faciliter l’accès aux soins.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le contrat d'accès aux soins (CAS), remplacée récemment par l'option pratique tarifaire maîtrisée (OPTAM).</t>
+  </si>
+  <si>
+    <t>Synonyme : optionContratAccesSoins, optionPratiqueTarifaireMaîtrisée</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-ext-practitionerrole-vitale-accepted</t>
+  </si>
+  <si>
+    <t>as-ext-practitionerrole-vitale-accepted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
+</t>
+  </si>
+  <si>
+    <t>L’indicateur Carte Vitale acceptée précisant si le professionnel, dans le cadre de cette situation opérationnelle, dispose des moyens techniques pour prendre en charge la carte vitale ou pas.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire l’indicateur Carte Vitale acceptée (oui/non).</t>
+  </si>
+  <si>
+    <t>Synonyme : carteVitaleAcceptee, optionPratiqueTarifaireMaîtrisée</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -550,7 +640,7 @@
     <t>Business Identifiers that are specific to a role/location.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idFonctionnel</t>
+    <t>Synonyme : idFonctionnel</t>
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
@@ -733,7 +823,7 @@
 </t>
   </si>
   <si>
-    <t>La sitation d'exercice est-elle active? (active | inactive)</t>
+    <t>La situation d'exercice est-elle active? (active | inactive)</t>
   </si>
   <si>
     <t>Whether this practitioner role record is in active use.</t>
@@ -779,7 +869,7 @@
     <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateDebutActivite</t>
+    <t>Synonyme : dateDebutActivite</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -1160,10 +1250,10 @@
 </t>
   </si>
   <si>
-    <t>Concept - reference to a terminology or just  text</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
+    <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation</t>
+  </si>
+  <si>
+    <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation.</t>
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
@@ -1189,9 +1279,6 @@
   </si>
   <si>
     <t>Activité ponctuelle du professionnel de type expertise.</t>
-  </si>
-  <si>
-    <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation.</t>
   </si>
   <si>
     <t>Synonyme : attributionParticuliere</t>
@@ -1888,12 +1975,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ84"/>
+  <dimension ref="A1:AJ89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.15625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1901,7 +1988,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.7265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2972,7 +3059,7 @@
         <v>72</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
@@ -3180,7 +3267,7 @@
         <v>72</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3200,9 +3287,7 @@
       <c r="M13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>71</v>
@@ -3268,13 +3353,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>71</v>
@@ -3284,7 +3369,7 @@
         <v>72</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3296,16 +3381,16 @@
         <v>71</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3372,14 +3457,16 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3389,29 +3476,25 @@
         <v>73</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>71</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>164</v>
       </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>71</v>
       </c>
@@ -3447,19 +3530,19 @@
         <v>71</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>72</v>
@@ -3476,12 +3559,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>71</v>
       </c>
@@ -3490,7 +3575,7 @@
         <v>72</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
@@ -3499,7 +3584,7 @@
         <v>71</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>167</v>
@@ -3513,9 +3598,7 @@
       <c r="N16" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>71</v>
       </c>
@@ -3563,7 +3646,7 @@
         <v>71</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>72</v>
@@ -3575,17 +3658,19 @@
         <v>90</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="B17" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>71</v>
       </c>
@@ -3597,7 +3682,7 @@
         <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>71</v>
@@ -3614,7 +3699,9 @@
       <c r="M17" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>71</v>
@@ -3663,19 +3750,19 @@
         <v>71</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3683,21 +3770,23 @@
         <v>177</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>71</v>
@@ -3706,16 +3795,16 @@
         <v>71</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3753,19 +3842,19 @@
         <v>71</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>72</v>
@@ -3782,12 +3871,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>71</v>
       </c>
@@ -3799,29 +3890,27 @@
         <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>71</v>
       </c>
@@ -3845,13 +3934,13 @@
         <v>71</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>187</v>
+        <v>71</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>71</v>
@@ -3869,19 +3958,19 @@
         <v>71</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3893,38 +3982,38 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>71</v>
@@ -3949,51 +4038,51 @@
         <v>71</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>195</v>
+        <v>71</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4004,10 +4093,10 @@
         <v>72</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>71</v>
@@ -4016,19 +4105,19 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>93</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>71</v>
@@ -4041,7 +4130,7 @@
         <v>71</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>71</v>
@@ -4077,13 +4166,13 @@
         <v>71</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>90</v>
@@ -4094,10 +4183,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4117,20 +4206,18 @@
         <v>71</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>71</v>
@@ -4143,7 +4230,7 @@
         <v>71</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>71</v>
@@ -4179,7 +4266,7 @@
         <v>71</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>72</v>
@@ -4188,29 +4275,29 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>71</v>
@@ -4219,19 +4306,19 @@
         <v>71</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>123</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>124</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4269,39 +4356,39 @@
         <v>71</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>218</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4318,24 +4405,26 @@
         <v>71</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>71</v>
       </c>
@@ -4359,13 +4448,13 @@
         <v>71</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>71</v>
@@ -4383,7 +4472,7 @@
         <v>71</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
@@ -4395,15 +4484,15 @@
         <v>90</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4417,7 +4506,7 @@
         <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>71</v>
@@ -4426,26 +4515,24 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q25" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
         <v>71</v>
       </c>
@@ -4465,13 +4552,13 @@
         <v>71</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>71</v>
+        <v>223</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>71</v>
+        <v>225</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>71</v>
@@ -4506,10 +4593,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4523,7 +4610,7 @@
         <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>71</v>
@@ -4532,19 +4619,19 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>213</v>
+        <v>93</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>71</v>
@@ -4557,7 +4644,7 @@
         <v>71</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>71</v>
+        <v>232</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>71</v>
@@ -4605,15 +4692,15 @@
         <v>90</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>218</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4633,18 +4720,20 @@
         <v>71</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>71</v>
@@ -4657,7 +4746,7 @@
         <v>71</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>71</v>
+        <v>238</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>71</v>
@@ -4693,7 +4782,7 @@
         <v>71</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>72</v>
@@ -4702,29 +4791,29 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>71</v>
@@ -4733,19 +4822,19 @@
         <v>71</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>124</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4783,39 +4872,39 @@
         <v>71</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>131</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4838,16 +4927,16 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4897,7 +4986,7 @@
         <v>71</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
@@ -4906,18 +4995,18 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>91</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4931,7 +5020,7 @@
         <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>71</v>
@@ -4940,23 +5029,25 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>71</v>
@@ -5001,7 +5092,7 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
@@ -5010,7 +5101,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>91</v>
@@ -5018,10 +5109,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5044,18 +5135,20 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>71</v>
       </c>
@@ -5103,7 +5196,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5115,15 +5208,15 @@
         <v>90</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5137,26 +5230,24 @@
         <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>71</v>
@@ -5205,7 +5296,7 @@
         <v>71</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
@@ -5214,22 +5305,22 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>225</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5245,23 +5336,21 @@
         <v>71</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>263</v>
+        <v>124</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>71</v>
       </c>
@@ -5285,31 +5374,31 @@
         <v>71</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
@@ -5321,15 +5410,15 @@
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5349,18 +5438,20 @@
         <v>71</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>71</v>
@@ -5409,7 +5500,7 @@
         <v>71</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>176</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5418,29 +5509,29 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>71</v>
+        <v>273</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>71</v>
@@ -5449,25 +5540,27 @@
         <v>71</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>123</v>
+        <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>124</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>126</v>
+        <v>277</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q35" s="2"/>
+      <c r="Q35" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="R35" t="s" s="2">
         <v>71</v>
       </c>
@@ -5499,39 +5592,39 @@
         <v>71</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>90</v>
+        <v>273</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5542,10 +5635,10 @@
         <v>72</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>71</v>
@@ -5554,20 +5647,18 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>71</v>
       </c>
@@ -5603,41 +5694,41 @@
         <v>71</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AC36" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD36" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>91</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>71</v>
       </c>
@@ -5658,20 +5749,18 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>71</v>
       </c>
@@ -5695,13 +5784,13 @@
         <v>71</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>71</v>
@@ -5719,31 +5808,29 @@
         <v>71</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>91</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>71</v>
       </c>
@@ -5752,10 +5839,10 @@
         <v>72</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>71</v>
@@ -5764,19 +5851,19 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>272</v>
+        <v>218</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>71</v>
@@ -5801,31 +5888,31 @@
         <v>71</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>72</v>
@@ -5837,19 +5924,17 @@
         <v>90</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>71</v>
       </c>
@@ -5861,29 +5946,25 @@
         <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>71</v>
       </c>
@@ -5907,13 +5988,13 @@
         <v>71</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>71</v>
@@ -5931,65 +6012,61 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>204</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>124</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>274</v>
+        <v>206</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>71</v>
       </c>
@@ -6013,31 +6090,31 @@
         <v>71</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>207</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>72</v>
@@ -6049,19 +6126,17 @@
         <v>90</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>71</v>
       </c>
@@ -6070,10 +6145,10 @@
         <v>72</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>71</v>
@@ -6082,19 +6157,19 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>71</v>
@@ -6119,31 +6194,29 @@
         <v>71</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB41" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>71</v>
-      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>72</v>
@@ -6160,13 +6233,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>71</v>
@@ -6188,19 +6261,19 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>71</v>
@@ -6225,13 +6298,13 @@
         <v>71</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>71</v>
@@ -6249,7 +6322,7 @@
         <v>71</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6266,13 +6339,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>71</v>
@@ -6294,19 +6367,19 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>71</v>
@@ -6331,13 +6404,13 @@
         <v>71</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>71</v>
@@ -6355,7 +6428,7 @@
         <v>71</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>72</v>
@@ -6372,13 +6445,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>71</v>
@@ -6400,19 +6473,19 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>71</v>
@@ -6437,13 +6510,13 @@
         <v>71</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>71</v>
@@ -6461,7 +6534,7 @@
         <v>71</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>72</v>
@@ -6481,7 +6554,7 @@
         <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>325</v>
@@ -6506,19 +6579,19 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>327</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>71</v>
@@ -6543,13 +6616,13 @@
         <v>71</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y45" t="s" s="2">
         <v>328</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -6567,7 +6640,7 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
@@ -6584,13 +6657,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>71</v>
@@ -6612,19 +6685,19 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="O46" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>71</v>
@@ -6649,13 +6722,13 @@
         <v>71</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>71</v>
@@ -6673,7 +6746,7 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
@@ -6690,13 +6763,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>71</v>
@@ -6718,19 +6791,19 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -6755,13 +6828,13 @@
         <v>71</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>71</v>
@@ -6779,7 +6852,7 @@
         <v>71</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -6796,13 +6869,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>71</v>
@@ -6824,19 +6897,19 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>71</v>
@@ -6861,13 +6934,13 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -6885,7 +6958,7 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
@@ -6902,13 +6975,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>71</v>
@@ -6930,19 +7003,19 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>71</v>
@@ -6967,13 +7040,13 @@
         <v>71</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>71</v>
@@ -6991,7 +7064,7 @@
         <v>71</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>72</v>
@@ -7008,13 +7081,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>71</v>
@@ -7036,19 +7109,19 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>71</v>
@@ -7073,13 +7146,13 @@
         <v>71</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>71</v>
@@ -7097,7 +7170,7 @@
         <v>71</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>72</v>
@@ -7114,13 +7187,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>71</v>
@@ -7142,19 +7215,19 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>71</v>
@@ -7179,13 +7252,13 @@
         <v>71</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>71</v>
@@ -7203,7 +7276,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7220,12 +7293,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>71</v>
       </c>
@@ -7237,7 +7312,7 @@
         <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>71</v>
@@ -7246,19 +7321,19 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>71</v>
@@ -7283,13 +7358,13 @@
         <v>71</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>71</v>
+        <v>368</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>71</v>
+        <v>369</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>71</v>
@@ -7307,13 +7382,13 @@
         <v>71</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>90</v>
@@ -7324,12 +7399,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>71</v>
       </c>
@@ -7338,10 +7415,10 @@
         <v>72</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>71</v>
@@ -7350,18 +7427,20 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>71</v>
       </c>
@@ -7385,31 +7464,31 @@
         <v>71</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>373</v>
+        <v>71</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>374</v>
+        <v>71</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>72</v>
@@ -7426,13 +7505,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>71</v>
@@ -7442,7 +7521,7 @@
         <v>72</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -7454,18 +7533,20 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>71</v>
       </c>
@@ -7489,11 +7570,13 @@
         <v>71</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>71</v>
@@ -7511,7 +7594,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7528,13 +7611,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>71</v>
@@ -7544,7 +7627,7 @@
         <v>72</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -7556,18 +7639,20 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>71</v>
       </c>
@@ -7591,13 +7676,13 @@
         <v>71</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>71</v>
@@ -7615,7 +7700,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7632,13 +7717,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -7648,7 +7733,7 @@
         <v>72</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -7660,18 +7745,20 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
       </c>
@@ -7695,13 +7782,13 @@
         <v>71</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>71</v>
@@ -7719,7 +7806,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -7736,14 +7823,12 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>71</v>
       </c>
@@ -7752,10 +7837,10 @@
         <v>72</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>71</v>
@@ -7764,18 +7849,20 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>71</v>
       </c>
@@ -7799,13 +7886,13 @@
         <v>71</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>396</v>
+        <v>71</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>386</v>
+        <v>71</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>71</v>
@@ -7823,13 +7910,13 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>90</v>
@@ -7840,14 +7927,12 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>71</v>
       </c>
@@ -7859,7 +7944,7 @@
         <v>73</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>71</v>
@@ -7868,16 +7953,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7903,31 +7988,31 @@
         <v>71</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="AC58" t="s" s="2">
-        <v>71</v>
+        <v>402</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -7944,13 +8029,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>71</v>
@@ -7972,16 +8057,16 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8007,13 +8092,11 @@
         <v>71</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>71</v>
@@ -8031,7 +8114,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8048,13 +8131,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8076,16 +8159,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8111,13 +8194,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8135,7 +8218,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8152,13 +8235,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>71</v>
@@ -8180,16 +8263,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8215,13 +8298,13 @@
         <v>71</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>71</v>
@@ -8239,7 +8322,7 @@
         <v>71</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>72</v>
@@ -8256,13 +8339,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>71</v>
@@ -8284,16 +8367,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8319,13 +8402,13 @@
         <v>71</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>71</v>
@@ -8343,7 +8426,7 @@
         <v>71</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>72</v>
@@ -8360,13 +8443,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>71</v>
@@ -8388,16 +8471,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8423,13 +8506,13 @@
         <v>71</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>71</v>
@@ -8447,7 +8530,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8464,13 +8547,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>71</v>
@@ -8492,16 +8575,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8527,13 +8610,13 @@
         <v>71</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>71</v>
@@ -8551,7 +8634,7 @@
         <v>71</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>72</v>
@@ -8568,12 +8651,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>71</v>
       </c>
@@ -8594,13 +8679,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>436</v>
+        <v>397</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>437</v>
@@ -8629,13 +8714,13 @@
         <v>71</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>71</v>
+        <v>438</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>71</v>
+        <v>413</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>71</v>
@@ -8653,7 +8738,7 @@
         <v>71</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>433</v>
+        <v>394</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>72</v>
@@ -8665,17 +8750,19 @@
         <v>90</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>71</v>
       </c>
@@ -8693,16 +8780,16 @@
         <v>71</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>439</v>
+        <v>218</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>442</v>
@@ -8731,13 +8818,13 @@
         <v>71</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>71</v>
+        <v>443</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>71</v>
+        <v>413</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>71</v>
@@ -8755,7 +8842,7 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
@@ -8767,17 +8854,19 @@
         <v>90</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>71</v>
       </c>
@@ -8798,18 +8887,18 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>444</v>
+        <v>218</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>447</v>
       </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>71</v>
       </c>
@@ -8833,29 +8922,31 @@
         <v>71</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>71</v>
+        <v>448</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>71</v>
+        <v>413</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -8867,18 +8958,18 @@
         <v>90</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>449</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>71</v>
@@ -8891,29 +8982,27 @@
         <v>73</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>71</v>
       </c>
@@ -8937,13 +9026,13 @@
         <v>71</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>71</v>
+        <v>453</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>71</v>
+        <v>413</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>71</v>
@@ -8961,7 +9050,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -8973,17 +9062,19 @@
         <v>90</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>449</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>71</v>
       </c>
@@ -9001,19 +9092,19 @@
         <v>71</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9039,13 +9130,13 @@
         <v>71</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>71</v>
+        <v>458</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>71</v>
+        <v>459</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>71</v>
@@ -9063,7 +9154,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>394</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9094,27 +9185,29 @@
         <v>72</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>173</v>
+        <v>461</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>174</v>
+        <v>462</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>71</v>
@@ -9163,31 +9256,31 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>176</v>
+        <v>460</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>71</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9197,7 +9290,7 @@
         <v>73</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>71</v>
@@ -9206,16 +9299,16 @@
         <v>71</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>123</v>
+        <v>466</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>124</v>
+        <v>467</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>178</v>
+        <v>468</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>126</v>
+        <v>469</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9253,19 +9346,19 @@
         <v>71</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>179</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9277,19 +9370,19 @@
         <v>90</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>131</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>463</v>
+        <v>71</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9299,28 +9392,26 @@
         <v>73</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>123</v>
+        <v>471</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>164</v>
+        <v>474</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>71</v>
@@ -9357,19 +9448,17 @@
         <v>71</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="AC72" s="2"/>
       <c r="AD72" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9381,17 +9470,19 @@
         <v>90</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>131</v>
+        <v>476</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
       </c>
@@ -9412,18 +9503,20 @@
         <v>71</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>99</v>
+        <v>479</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>71</v>
       </c>
@@ -9447,13 +9540,13 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>471</v>
+        <v>71</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>472</v>
+        <v>71</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>71</v>
@@ -9471,7 +9564,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9483,15 +9576,15 @@
         <v>90</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>91</v>
+        <v>476</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9502,10 +9595,10 @@
         <v>72</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>71</v>
@@ -9514,15 +9607,17 @@
         <v>71</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>227</v>
+        <v>483</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>71</v>
@@ -9571,13 +9666,13 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>90</v>
@@ -9588,10 +9683,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9614,17 +9709,15 @@
         <v>71</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>477</v>
+        <v>201</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>478</v>
+        <v>202</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>71</v>
@@ -9673,7 +9766,7 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>476</v>
+        <v>204</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
@@ -9682,29 +9775,29 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>71</v>
@@ -9716,16 +9809,16 @@
         <v>71</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>477</v>
+        <v>123</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>482</v>
+        <v>124</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>483</v>
+        <v>206</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>480</v>
+        <v>126</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9763,43 +9856,43 @@
         <v>71</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>481</v>
+        <v>207</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>71</v>
+        <v>490</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -9809,25 +9902,29 @@
         <v>73</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I77" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="J77" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>71</v>
       </c>
@@ -9875,7 +9972,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -9887,15 +9984,15 @@
         <v>90</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9906,7 +10003,7 @@
         <v>72</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>71</v>
@@ -9918,15 +10015,17 @@
         <v>71</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>174</v>
+        <v>495</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>71</v>
@@ -9951,13 +10050,13 @@
         <v>71</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>71</v>
+        <v>498</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>71</v>
+        <v>499</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>71</v>
@@ -9975,38 +10074,38 @@
         <v>71</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>176</v>
+        <v>494</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>71</v>
@@ -10018,17 +10117,15 @@
         <v>71</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>124</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>71</v>
@@ -10065,75 +10162,73 @@
         <v>71</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>179</v>
+        <v>500</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>463</v>
+        <v>71</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>123</v>
+        <v>504</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>71</v>
       </c>
@@ -10181,27 +10276,27 @@
         <v>71</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10209,7 +10304,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>78</v>
@@ -10224,16 +10319,16 @@
         <v>71</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>173</v>
+        <v>504</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10283,10 +10378,10 @@
         <v>71</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
@@ -10300,10 +10395,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10314,10 +10409,10 @@
         <v>72</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>71</v>
@@ -10326,17 +10421,15 @@
         <v>71</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>213</v>
+        <v>483</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>71</v>
@@ -10385,27 +10478,27 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>218</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10419,7 +10512,7 @@
         <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>71</v>
@@ -10428,17 +10521,15 @@
         <v>71</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>497</v>
+        <v>202</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10487,7 +10578,7 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>496</v>
+        <v>204</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
@@ -10496,22 +10587,22 @@
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10521,7 +10612,7 @@
         <v>73</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>71</v>
@@ -10530,20 +10621,18 @@
         <v>71</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>501</v>
+        <v>124</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>502</v>
+        <v>206</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>71</v>
       </c>
@@ -10579,19 +10668,19 @@
         <v>71</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>499</v>
+        <v>207</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
@@ -10603,11 +10692,525 @@
         <v>90</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ84">
+  <autoFilter ref="A1:AJ89">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10617,7 +11220,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T10:09:07+00:00</t>
+    <t>2023-06-08T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -295,17 +295,207 @@
 </t>
   </si>
   <si>
+    <t>PractitionerRole.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension:as-data-trace</t>
+  </si>
+  <si>
+    <t>as-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace</t>
+  </si>
+  <si>
+    <t>Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI))..</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>PractitionerRole.implicitRules</t>
+    <t>PractitionerRole.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>PractitionerRole.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -395,38 +585,10 @@
     <t>PractitionerRole.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>PractitionerRole.extension:serviceTypeDuration</t>
@@ -451,7 +613,7 @@
     <t>as-ext-practitionerrole-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
 </t>
   </si>
   <si>
@@ -470,7 +632,7 @@
     <t>as-ext-practitionerrole-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
 </t>
   </si>
   <si>
@@ -489,7 +651,7 @@
     <t>as-ext-practitionerrole-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
 </t>
   </si>
   <si>
@@ -505,7 +667,7 @@
     <t>as-ext-practitionerrole-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
 </t>
   </si>
   <si>
@@ -525,7 +687,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
 </t>
   </si>
   <si>
@@ -541,7 +703,7 @@
     <t>as-ext-practitionerrole-end-cause</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
 </t>
   </si>
   <si>
@@ -560,7 +722,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
 </t>
   </si>
   <si>
@@ -579,7 +741,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
 </t>
   </si>
   <si>
@@ -598,7 +760,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
 </t>
   </si>
   <si>
@@ -649,26 +811,7 @@
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.use</t>
@@ -717,9 +860,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -959,10 +1099,6 @@
     <t>PractitionerRole.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Code defined by a terminology system</t>
   </si>
   <si>
@@ -1246,7 +1382,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
 </t>
   </si>
   <si>
@@ -1505,7 +1641,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>
@@ -1975,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ89"/>
+  <dimension ref="A1:AJ98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
@@ -1988,7 +2124,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="108.7421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2424,15 +2560,15 @@
         <v>90</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2449,23 +2585,21 @@
         <v>71</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="M5" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>71</v>
@@ -2514,7 +2648,7 @@
         <v>71</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>72</v>
@@ -2523,29 +2657,29 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>71</v>
@@ -2557,16 +2691,16 @@
         <v>71</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2592,43 +2726,43 @@
         <v>71</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" hidden="true">
@@ -2636,11 +2770,13 @@
         <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="D7" t="s" s="2">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2650,7 +2786,7 @@
         <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>71</v>
@@ -2667,9 +2803,7 @@
       <c r="M7" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="N7" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>71</v>
@@ -2718,38 +2852,38 @@
         <v>71</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>71</v>
@@ -2758,19 +2892,19 @@
         <v>71</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2820,38 +2954,38 @@
         <v>71</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>71</v>
@@ -2860,19 +2994,19 @@
         <v>71</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2910,52 +3044,50 @@
         <v>71</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>71</v>
@@ -2964,19 +3096,19 @@
         <v>71</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3026,31 +3158,29 @@
         <v>71</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>71</v>
       </c>
@@ -3062,25 +3192,25 @@
         <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3130,7 +3260,7 @@
         <v>71</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>72</v>
@@ -3142,19 +3272,17 @@
         <v>90</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>71</v>
       </c>
@@ -3166,25 +3294,25 @@
         <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3210,13 +3338,13 @@
         <v>71</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>71</v>
@@ -3234,7 +3362,7 @@
         <v>71</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>72</v>
@@ -3246,19 +3374,17 @@
         <v>90</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>71</v>
       </c>
@@ -3270,24 +3396,26 @@
         <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I13" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>71</v>
@@ -3312,13 +3440,13 @@
         <v>71</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>71</v>
@@ -3336,7 +3464,7 @@
         <v>71</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>72</v>
@@ -3348,19 +3476,17 @@
         <v>90</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>71</v>
       </c>
@@ -3369,28 +3495,28 @@
         <v>72</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3440,31 +3566,29 @@
         <v>71</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>71</v>
       </c>
@@ -3473,10 +3597,10 @@
         <v>72</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>71</v>
@@ -3485,15 +3609,17 @@
         <v>71</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>71</v>
@@ -3518,13 +3644,13 @@
         <v>71</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>71</v>
@@ -3542,33 +3668,31 @@
         <v>71</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3578,7 +3702,7 @@
         <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>71</v>
@@ -3587,16 +3711,16 @@
         <v>71</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3646,43 +3770,41 @@
         <v>71</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>71</v>
@@ -3691,16 +3813,16 @@
         <v>71</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3750,7 +3872,7 @@
         <v>71</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>72</v>
@@ -3759,34 +3881,32 @@
         <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>71</v>
@@ -3795,16 +3915,16 @@
         <v>71</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3842,19 +3962,19 @@
         <v>71</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>72</v>
@@ -3866,31 +3986,31 @@
         <v>90</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>71</v>
@@ -3899,16 +4019,16 @@
         <v>71</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3958,7 +4078,7 @@
         <v>71</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>72</v>
@@ -3970,7 +4090,7 @@
         <v>90</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3978,11 +4098,13 @@
         <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3992,29 +4114,27 @@
         <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>71</v>
       </c>
@@ -4050,19 +4170,19 @@
         <v>71</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>72</v>
@@ -4074,17 +4194,19 @@
         <v>90</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>71</v>
       </c>
@@ -4102,23 +4224,21 @@
         <v>71</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>71</v>
       </c>
@@ -4166,7 +4286,7 @@
         <v>71</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>72</v>
@@ -4178,17 +4298,19 @@
         <v>90</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>71</v>
       </c>
@@ -4197,10 +4319,10 @@
         <v>72</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>71</v>
@@ -4209,13 +4331,13 @@
         <v>71</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4266,31 +4388,33 @@
         <v>71</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4300,7 +4424,7 @@
         <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>71</v>
@@ -4309,16 +4433,16 @@
         <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4356,19 +4480,19 @@
         <v>71</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>72</v>
@@ -4380,17 +4504,19 @@
         <v>90</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>71</v>
       </c>
@@ -4399,32 +4525,28 @@
         <v>72</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>71</v>
       </c>
@@ -4448,13 +4570,13 @@
         <v>71</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>215</v>
+        <v>71</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>71</v>
@@ -4472,19 +4594,19 @@
         <v>71</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4492,9 +4614,11 @@
         <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>71</v>
       </c>
@@ -4506,29 +4630,27 @@
         <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O25" t="s" s="2">
         <v>222</v>
       </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>71</v>
       </c>
@@ -4552,13 +4674,13 @@
         <v>71</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>71</v>
@@ -4576,29 +4698,31 @@
         <v>71</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>71</v>
       </c>
@@ -4610,29 +4734,27 @@
         <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>71</v>
       </c>
@@ -4644,7 +4766,7 @@
         <v>71</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>71</v>
@@ -4680,29 +4802,31 @@
         <v>71</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>71</v>
       </c>
@@ -4714,25 +4838,25 @@
         <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4746,7 +4870,7 @@
         <v>71</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>238</v>
+        <v>71</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>71</v>
@@ -4782,29 +4906,31 @@
         <v>71</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>71</v>
       </c>
@@ -4816,25 +4942,25 @@
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4884,61 +5010,63 @@
         <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>246</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>98</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>71</v>
       </c>
@@ -4974,39 +5102,39 @@
         <v>71</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>253</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5017,7 +5145,7 @@
         <v>72</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5029,26 +5157,24 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q30" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
         <v>71</v>
       </c>
@@ -5092,27 +5218,27 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5126,29 +5252,25 @@
         <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>241</v>
+        <v>92</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>93</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>71</v>
       </c>
@@ -5196,7 +5318,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>95</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5205,29 +5327,29 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>246</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>71</v>
@@ -5239,15 +5361,17 @@
         <v>71</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>71</v>
@@ -5284,73 +5408,75 @@
         <v>71</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>124</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>71</v>
       </c>
@@ -5374,51 +5500,51 @@
         <v>71</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>71</v>
+        <v>260</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>71</v>
+        <v>261</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5441,18 +5567,20 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>71</v>
       </c>
@@ -5476,13 +5604,13 @@
         <v>71</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>71</v>
+        <v>269</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>71</v>
@@ -5500,7 +5628,7 @@
         <v>71</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5509,18 +5637,18 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>273</v>
+        <v>90</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5543,68 +5671,68 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="P35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T35" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q35" t="s" s="2">
+      <c r="U35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
@@ -5613,18 +5741,18 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>273</v>
+        <v>90</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5638,7 +5766,7 @@
         <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>71</v>
@@ -5647,16 +5775,16 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5670,7 +5798,7 @@
         <v>71</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>71</v>
+        <v>283</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>71</v>
@@ -5706,7 +5834,7 @@
         <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
@@ -5718,7 +5846,7 @@
         <v>90</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -5740,7 +5868,7 @@
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>71</v>
@@ -5808,7 +5936,7 @@
         <v>71</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>72</v>
@@ -5820,15 +5948,15 @@
         <v>90</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>253</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5839,7 +5967,7 @@
         <v>72</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>71</v>
@@ -5851,20 +5979,18 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>71</v>
       </c>
@@ -5888,13 +6014,13 @@
         <v>71</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>296</v>
+        <v>71</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>71</v>
@@ -5912,27 +6038,27 @@
         <v>71</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>71</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5946,29 +6072,35 @@
         <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>71</v>
       </c>
@@ -6012,7 +6144,7 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>204</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
@@ -6021,52 +6153,54 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>123</v>
+        <v>286</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>124</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>71</v>
       </c>
@@ -6102,39 +6236,39 @@
         <v>71</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>131</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6145,7 +6279,7 @@
         <v>72</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>71</v>
@@ -6154,23 +6288,19 @@
         <v>71</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>93</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>71</v>
       </c>
@@ -6206,75 +6336,73 @@
         <v>71</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>306</v>
+        <v>95</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>302</v>
+        <v>100</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>71</v>
       </c>
@@ -6298,31 +6426,31 @@
         <v>71</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>311</v>
+        <v>71</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>312</v>
+        <v>71</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6334,19 +6462,17 @@
         <v>90</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>71</v>
       </c>
@@ -6358,7 +6484,7 @@
         <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>71</v>
@@ -6367,20 +6493,18 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>71</v>
       </c>
@@ -6404,43 +6528,43 @@
         <v>71</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AG43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="AJ43" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -6448,11 +6572,9 @@
         <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>71</v>
       </c>
@@ -6464,7 +6586,7 @@
         <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>71</v>
@@ -6473,24 +6595,24 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>71</v>
       </c>
@@ -6510,55 +6632,53 @@
         <v>71</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>323</v>
+        <v>71</v>
       </c>
       <c r="Z44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AA44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="AJ44" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C45" t="s" s="2">
         <v>325</v>
       </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>71</v>
       </c>
@@ -6579,20 +6699,18 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>71</v>
       </c>
@@ -6616,13 +6734,13 @@
         <v>71</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>328</v>
+        <v>71</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>318</v>
+        <v>71</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -6640,31 +6758,29 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C46" t="s" s="2">
         <v>330</v>
       </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>71</v>
       </c>
@@ -6685,20 +6801,18 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>71</v>
       </c>
@@ -6722,13 +6836,13 @@
         <v>71</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>71</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>318</v>
+        <v>71</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>71</v>
@@ -6746,31 +6860,29 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C47" t="s" s="2">
         <v>335</v>
       </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>71</v>
       </c>
@@ -6779,10 +6891,10 @@
         <v>72</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>71</v>
@@ -6791,19 +6903,19 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -6828,13 +6940,13 @@
         <v>71</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>71</v>
@@ -6852,7 +6964,7 @@
         <v>71</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -6864,19 +6976,17 @@
         <v>90</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>71</v>
       </c>
@@ -6888,29 +6998,25 @@
         <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>342</v>
+        <v>93</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>71</v>
       </c>
@@ -6934,13 +7040,13 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>344</v>
+        <v>71</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>345</v>
+        <v>71</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -6958,65 +7064,61 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>95</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>99</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>302</v>
+        <v>100</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>71</v>
       </c>
@@ -7040,31 +7142,31 @@
         <v>71</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>350</v>
+        <v>71</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>351</v>
+        <v>71</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>72</v>
@@ -7076,19 +7178,17 @@
         <v>90</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>71</v>
       </c>
@@ -7097,10 +7197,10 @@
         <v>72</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>71</v>
@@ -7109,19 +7209,19 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>71</v>
@@ -7146,31 +7246,29 @@
         <v>71</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>356</v>
+        <v>71</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>357</v>
+        <v>71</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>72</v>
@@ -7182,18 +7280,18 @@
         <v>90</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>71</v>
@@ -7215,19 +7313,19 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>71</v>
@@ -7252,13 +7350,13 @@
         <v>71</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>71</v>
@@ -7276,7 +7374,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7288,18 +7386,18 @@
         <v>90</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>71</v>
@@ -7321,19 +7419,19 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>71</v>
@@ -7358,13 +7456,13 @@
         <v>71</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>71</v>
@@ -7382,7 +7480,7 @@
         <v>71</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>72</v>
@@ -7394,18 +7492,18 @@
         <v>90</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>71</v>
@@ -7427,19 +7525,19 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>71</v>
@@ -7464,13 +7562,13 @@
         <v>71</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>71</v>
@@ -7488,7 +7586,7 @@
         <v>71</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>72</v>
@@ -7500,18 +7598,18 @@
         <v>90</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>71</v>
@@ -7533,19 +7631,19 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>71</v>
@@ -7570,13 +7668,13 @@
         <v>71</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>71</v>
@@ -7594,7 +7692,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7606,18 +7704,18 @@
         <v>90</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>71</v>
@@ -7639,19 +7737,19 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>71</v>
@@ -7676,13 +7774,13 @@
         <v>71</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>71</v>
@@ -7700,7 +7798,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7712,18 +7810,18 @@
         <v>90</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -7745,19 +7843,19 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
@@ -7782,13 +7880,13 @@
         <v>71</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>71</v>
@@ -7806,7 +7904,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -7818,17 +7916,19 @@
         <v>90</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>71</v>
       </c>
@@ -7840,7 +7940,7 @@
         <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>71</v>
@@ -7849,19 +7949,19 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>71</v>
@@ -7886,13 +7986,13 @@
         <v>71</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>71</v>
+        <v>388</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>71</v>
+        <v>389</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>71</v>
@@ -7910,29 +8010,31 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>71</v>
       </c>
@@ -7941,10 +8043,10 @@
         <v>72</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>71</v>
@@ -7953,18 +8055,20 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>71</v>
       </c>
@@ -7988,31 +8092,31 @@
         <v>71</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>402</v>
+        <v>71</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -8024,18 +8128,18 @@
         <v>90</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>71</v>
@@ -8045,7 +8149,7 @@
         <v>72</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8057,18 +8161,20 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>71</v>
       </c>
@@ -8092,11 +8198,13 @@
         <v>71</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>71</v>
@@ -8114,7 +8222,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8126,18 +8234,18 @@
         <v>90</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8147,7 +8255,7 @@
         <v>72</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -8159,18 +8267,20 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>71</v>
       </c>
@@ -8194,13 +8304,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8218,7 +8328,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8230,18 +8340,18 @@
         <v>90</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>71</v>
@@ -8251,7 +8361,7 @@
         <v>72</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -8263,18 +8373,20 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>71</v>
       </c>
@@ -8298,10 +8410,10 @@
         <v>71</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>413</v>
@@ -8322,7 +8434,7 @@
         <v>71</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>72</v>
@@ -8334,18 +8446,18 @@
         <v>90</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>71</v>
@@ -8355,7 +8467,7 @@
         <v>72</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -8367,18 +8479,20 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>71</v>
       </c>
@@ -8402,10 +8516,10 @@
         <v>71</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>413</v>
@@ -8426,7 +8540,7 @@
         <v>71</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>72</v>
@@ -8438,18 +8552,18 @@
         <v>90</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>71</v>
@@ -8459,7 +8573,7 @@
         <v>72</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -8471,18 +8585,20 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>71</v>
       </c>
@@ -8506,10 +8622,10 @@
         <v>71</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="Z63" t="s" s="2">
         <v>413</v>
@@ -8530,7 +8646,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8542,18 +8658,18 @@
         <v>90</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>71</v>
@@ -8563,7 +8679,7 @@
         <v>72</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -8575,18 +8691,20 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>71</v>
       </c>
@@ -8610,13 +8728,13 @@
         <v>71</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>71</v>
@@ -8634,7 +8752,7 @@
         <v>71</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>72</v>
@@ -8646,18 +8764,18 @@
         <v>90</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>71</v>
@@ -8667,7 +8785,7 @@
         <v>72</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -8679,18 +8797,20 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>71</v>
       </c>
@@ -8714,13 +8834,13 @@
         <v>71</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>71</v>
@@ -8738,7 +8858,7 @@
         <v>71</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>72</v>
@@ -8750,19 +8870,17 @@
         <v>90</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>71</v>
       </c>
@@ -8771,10 +8889,10 @@
         <v>72</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>71</v>
@@ -8783,18 +8901,20 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>71</v>
       </c>
@@ -8818,13 +8938,13 @@
         <v>71</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>443</v>
+        <v>71</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>413</v>
+        <v>71</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>71</v>
@@ -8842,31 +8962,29 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>71</v>
       </c>
@@ -8878,7 +8996,7 @@
         <v>73</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>71</v>
@@ -8887,16 +9005,16 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8922,31 +9040,31 @@
         <v>71</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>413</v>
+        <v>444</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>71</v>
+        <v>445</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>71</v>
+        <v>446</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -8958,18 +9076,18 @@
         <v>90</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>71</v>
@@ -8991,16 +9109,16 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9026,13 +9144,11 @@
         <v>71</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>71</v>
@@ -9050,7 +9166,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -9062,18 +9178,18 @@
         <v>90</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>71</v>
@@ -9095,16 +9211,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9130,13 +9246,13 @@
         <v>71</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>71</v>
@@ -9154,7 +9270,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9166,17 +9282,19 @@
         <v>90</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>71</v>
       </c>
@@ -9197,16 +9315,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9232,13 +9350,13 @@
         <v>71</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>71</v>
+        <v>462</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>71</v>
@@ -9256,7 +9374,7 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
@@ -9268,17 +9386,19 @@
         <v>90</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>71</v>
       </c>
@@ -9296,19 +9416,19 @@
         <v>71</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9334,13 +9454,13 @@
         <v>71</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>71</v>
+        <v>467</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>71</v>
@@ -9358,7 +9478,7 @@
         <v>71</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9370,17 +9490,19 @@
         <v>90</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>71</v>
       </c>
@@ -9401,18 +9523,18 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L72" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>474</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>71</v>
       </c>
@@ -9436,29 +9558,31 @@
         <v>71</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>71</v>
+        <v>472</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AC72" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD72" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9470,18 +9594,18 @@
         <v>90</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>476</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
@@ -9494,29 +9618,27 @@
         <v>73</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>479</v>
+        <v>264</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>71</v>
       </c>
@@ -9540,13 +9662,13 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>71</v>
+        <v>477</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>71</v>
@@ -9564,7 +9686,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9576,17 +9698,19 @@
         <v>90</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>476</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>71</v>
       </c>
@@ -9604,19 +9728,19 @@
         <v>71</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>483</v>
+        <v>264</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9642,13 +9766,13 @@
         <v>71</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>71</v>
+        <v>482</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>71</v>
@@ -9666,7 +9790,7 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
@@ -9678,17 +9802,19 @@
         <v>90</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>71</v>
       </c>
@@ -9697,27 +9823,29 @@
         <v>72</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>202</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>71</v>
@@ -9742,13 +9870,13 @@
         <v>71</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>71</v>
+        <v>487</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>71</v>
@@ -9766,19 +9894,19 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>204</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -9786,11 +9914,13 @@
         <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="D76" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -9800,25 +9930,25 @@
         <v>73</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>124</v>
+        <v>490</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>206</v>
+        <v>441</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>126</v>
+        <v>491</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9844,31 +9974,31 @@
         <v>71</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>71</v>
+        <v>492</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>207</v>
+        <v>438</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
@@ -9880,19 +10010,21 @@
         <v>90</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="D77" t="s" s="2">
-        <v>490</v>
+        <v>71</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -9902,29 +10034,27 @@
         <v>73</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>71</v>
       </c>
@@ -9948,13 +10078,13 @@
         <v>71</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>71</v>
+        <v>497</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>71</v>
@@ -9972,7 +10102,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>493</v>
+        <v>438</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -9984,17 +10114,19 @@
         <v>90</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>71</v>
       </c>
@@ -10006,25 +10138,25 @@
         <v>73</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>99</v>
+        <v>264</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>496</v>
+        <v>441</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10050,13 +10182,13 @@
         <v>71</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>71</v>
@@ -10074,7 +10206,7 @@
         <v>71</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>494</v>
+        <v>438</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>72</v>
@@ -10086,15 +10218,15 @@
         <v>90</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10105,27 +10237,29 @@
         <v>72</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>255</v>
+        <v>505</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>71</v>
@@ -10174,27 +10308,27 @@
         <v>71</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10205,10 +10339,10 @@
         <v>72</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>71</v>
@@ -10217,16 +10351,16 @@
         <v>71</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10276,27 +10410,27 @@
         <v>71</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10307,30 +10441,30 @@
         <v>72</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>71</v>
       </c>
@@ -10366,41 +10500,41 @@
         <v>71</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="AC81" s="2"/>
       <c r="AD81" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>91</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>71</v>
       </c>
@@ -10412,7 +10546,7 @@
         <v>73</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>71</v>
@@ -10421,16 +10555,20 @@
         <v>71</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>483</v>
+        <v>523</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>71</v>
       </c>
@@ -10478,7 +10616,7 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
@@ -10490,15 +10628,15 @@
         <v>90</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>91</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10509,10 +10647,10 @@
         <v>72</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>71</v>
@@ -10521,15 +10659,17 @@
         <v>71</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>201</v>
+        <v>527</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>202</v>
+        <v>528</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10578,38 +10718,38 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>204</v>
+        <v>526</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>71</v>
@@ -10621,17 +10761,15 @@
         <v>71</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>71</v>
@@ -10668,43 +10806,43 @@
         <v>71</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>490</v>
+        <v>97</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -10717,26 +10855,24 @@
         <v>71</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>491</v>
+        <v>99</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>492</v>
+        <v>100</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>71</v>
       </c>
@@ -10772,19 +10908,19 @@
         <v>71</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>105</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>72</v>
@@ -10796,49 +10932,51 @@
         <v>90</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>71</v>
+        <v>534</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>71</v>
       </c>
@@ -10886,27 +11024,27 @@
         <v>71</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10917,7 +11055,7 @@
         <v>72</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>71</v>
@@ -10929,16 +11067,16 @@
         <v>71</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>244</v>
+        <v>541</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10964,13 +11102,13 @@
         <v>71</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>71</v>
+        <v>542</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>71</v>
+        <v>543</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>71</v>
@@ -10988,27 +11126,27 @@
         <v>71</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>246</v>
+        <v>117</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11022,7 +11160,7 @@
         <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>71</v>
@@ -11031,17 +11169,15 @@
         <v>71</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>71</v>
@@ -11090,7 +11226,7 @@
         <v>71</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>72</v>
@@ -11102,15 +11238,15 @@
         <v>90</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11121,10 +11257,10 @@
         <v>72</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>71</v>
@@ -11133,20 +11269,18 @@
         <v>71</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>71</v>
       </c>
@@ -11194,23 +11328,941 @@
         <v>71</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ89">
+  <autoFilter ref="A1:AJ98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11220,7 +12272,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:13:57+00:00</t>
+    <t>2023-06-15T09:14:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>PractitionerRole.meta.extension:as-data-trace</t>
-  </si>
-  <si>
-    <t>as-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t>PractitionerRole.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:14:52+00:00</t>
+    <t>2023-06-16T14:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1519,7 +1519,7 @@
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:code}
+    <t xml:space="preserve">profile:$this.resolve()}
 </t>
   </si>
   <si>
@@ -2032,7 +2032,7 @@
     <col min="25" max="25" width="168.7265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="107.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="54.1171875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-16T14:16:48+00:00</t>
+    <t>2023-07-03T12:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T12:37:47+00:00</t>
+    <t>2023-07-10T14:48:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:48:30+00:00</t>
+    <t>2023-07-10T14:51:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -688,13 +688,10 @@
 </t>
   </si>
   <si>
-    <t>identifiant métier calculé à partir des identifiants techniques de l'exercice professionnel et la situation d'exercice.</t>
+    <t>identifiant métier calculé à partir des identifiants techniques de l'exercice professionnel et la situation d'exercice (Synonyme : idFonctionnel).</t>
   </si>
   <si>
     <t>Business Identifiers that are specific to a role/location.</t>
-  </si>
-  <si>
-    <t>Synonyme : idFonctionnel</t>
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
@@ -786,13 +783,13 @@
     <t>PractitionerRole.identifier.value</t>
   </si>
   <si>
-    <t>Identifiant technique de l'activité.</t>
+    <t>Identifiant technique de l'activité (Synonyme : idActivite).</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>Synonyme : idActivite</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -895,13 +892,13 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de début de l’activité correspondant à la date d’installation en cabinet ou à la date d’embauche du salarié.</t>
+    <t>[Donnée restreinte] : Date de début de l’activité correspondant à la date d’installation en cabinet ou à la date d’embauche du salarié (Synonyme : dateDebutActivite).</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
-    <t>Synonyme : dateDebutActivite</t>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -914,13 +911,13 @@
     <t>PractitionerRole.period.end</t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de fin de l’activité.</t>
+    <t>[Donnée restreinte] : Date de fin de l’activité (Synonyme : dateFinActivite).</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
-    <t>Synonyme : dateFinActivite</t>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
@@ -936,13 +933,13 @@
 </t>
   </si>
   <si>
-    <t>Référence permettant de lier l’exercice professionnel et la situation d'exercice à un professionnel (Practitioner).</t>
+    <t>Référence permettant de lier l’exercice professionnel et la situation d'exercice à un professionnel (Practitioner). (Synonyme : idPP)</t>
   </si>
   <si>
     <t>Practitioner that is able to provide the defined services for the organization.</t>
   </si>
   <si>
-    <t>Synonyme : idPP</t>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>PractitionerRole.organization</t>
@@ -952,13 +949,10 @@
 </t>
   </si>
   <si>
-    <t>Référence vers l’EG ou EJ de rattachement de la situation d’exercice (Organization)</t>
+    <t>Référence vers l’EG ou EJ de rattachement de la situation d’exercice (Organization) (Synonyme : idNat_Struct)</t>
   </si>
   <si>
     <t>The organization where the Practitioner performs the roles associated.</t>
-  </si>
-  <si>
-    <t>Synonyme : idNat_Strcut</t>
   </si>
   <si>
     <t>PractitionerRole.code</t>
@@ -1016,10 +1010,7 @@
     <t>CategorieProfession</t>
   </si>
   <si>
-    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant.</t>
-  </si>
-  <si>
-    <t>Synonyme : categorieProfessionnelle</t>
+    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (Synonyme : categorieProfessionnelle).</t>
   </si>
   <si>
     <t>Liste des catégories professionnelles</t>
@@ -1034,10 +1025,7 @@
     <t>professionG15</t>
   </si>
   <si>
-    <t>Profession exercée ou future profession de l'étudiant.</t>
-  </si>
-  <si>
-    <t>Synonyme : professionSante</t>
+    <t>Profession exercée ou future profession de l'étudiant (Synonyme : professionSante).</t>
   </si>
   <si>
     <t>Liste des professions de santé  définies par le code de la santé publique</t>
@@ -1052,10 +1040,7 @@
     <t>professionR94</t>
   </si>
   <si>
-    <t>Profession du social.</t>
-  </si>
-  <si>
-    <t>Synonyme : professionSocial</t>
+    <t>Profession du social (Synonyme : professionSocial).</t>
   </si>
   <si>
     <t>Liste des professions du social</t>
@@ -1067,10 +1052,7 @@
     <t>professionR95</t>
   </si>
   <si>
-    <t>Profession à usage de titre professionnel.</t>
-  </si>
-  <si>
-    <t>Synonyme : usagerTitre</t>
+    <t>Profession à usage de titre professionnel (Synonyme : usagerTitre).</t>
   </si>
   <si>
     <t>Liste des professions à usage de titre professionnel</t>
@@ -1082,10 +1064,7 @@
     <t>professionR291</t>
   </si>
   <si>
-    <t>professionnel non membre d'une profession réglementée.</t>
-  </si>
-  <si>
-    <t>Synonyme : autreProfession</t>
+    <t>professionnel non membre d'une profession réglementée (Synonyme : autreProfession).</t>
   </si>
   <si>
     <t>Liste de professionnels non membres d'une profession réglementée</t>
@@ -1097,10 +1076,7 @@
     <t>genreActivite</t>
   </si>
   <si>
-    <t>Le genre identifiant une activité qui nécessite l’application de règles de gestion spécifiques.</t>
-  </si>
-  <si>
-    <t>Synonyme : genreActivite</t>
+    <t>Le genre identifiant une activité qui nécessite l’application de règles de gestion spécifiques (Synonyme : genreActivite).</t>
   </si>
   <si>
     <t>Liste des genres d'activité</t>
@@ -1115,10 +1091,7 @@
     <t>modeExercice</t>
   </si>
   <si>
-    <t>Le mode d'exercice décrit selon quelle modalité une activité est exercée au regard de l'organisation de la rétribution du professionnel.</t>
-  </si>
-  <si>
-    <t>Synonyme : modeExercice</t>
+    <t>Le mode d'exercice décrit selon quelle modalité une activité est exercée au regard de l'organisation de la rétribution du professionnel (Synonyme : modeExercice).</t>
   </si>
   <si>
     <t>Liste des modes d'exercice</t>
@@ -1133,10 +1106,7 @@
     <t>typeActiviteLiberale</t>
   </si>
   <si>
-    <t>Type d’activité libérale, par exemple: Cabinet; Secteur privé à l'hôpital.</t>
-  </si>
-  <si>
-    <t>Synonyme : typeActiviteLiberale</t>
+    <t>Type d’activité libérale, par exemple: Cabinet; Secteur privé à l'hôpital (Synonyme : typeActiviteLiberale).</t>
   </si>
   <si>
     <t>Liste des types d’activité</t>
@@ -1151,10 +1121,7 @@
     <t>statutProfessionnelSSA</t>
   </si>
   <si>
-    <t>Statut du professionnel du Service de santé des armées.</t>
-  </si>
-  <si>
-    <t>Synonyme : statutProfessionnelSSA</t>
+    <t>Statut du professionnel du Service de santé des armées (Synonyme : statutProfessionnelSSA).</t>
   </si>
   <si>
     <t>Liste des statuts SSA</t>
@@ -1169,10 +1136,7 @@
     <t>statutHospitalier</t>
   </si>
   <si>
-    <t>Statut hospitalier dans le cas d’une activité exercée en établissement public de santé.</t>
-  </si>
-  <si>
-    <t>Synonyme : statutHospitalier</t>
+    <t>Statut hospitalier dans le cas d’une activité exercée en établissement public de santé (Synonyme : statutHospitalier).</t>
   </si>
   <si>
     <t>Liste des statuts hospitaliers</t>
@@ -1187,10 +1151,7 @@
     <t>fonctionR21</t>
   </si>
   <si>
-    <t>Fonction du professionnel au sein de la structure d’exercice.</t>
-  </si>
-  <si>
-    <t>Synonyme : role</t>
+    <t>Fonction du professionnel au sein de la structure d’exercice (Synonyme : role).</t>
   </si>
   <si>
     <t>Liste des fonctions et rôles</t>
@@ -1205,7 +1166,7 @@
     <t>fonctionR96</t>
   </si>
   <si>
-    <t>Autre fonction du domaine sanitaire exercée par le professionnel au sein de la structure d’exercice.</t>
+    <t>Autre fonction du domaine sanitaire exercée par le professionnel au sein de la structure d’exercice (Synonyme : role).</t>
   </si>
   <si>
     <t>PractitionerRole.code.coding:fonctionR85</t>
@@ -1214,7 +1175,7 @@
     <t>fonctionR85</t>
   </si>
   <si>
-    <t>Rôle du professionnel dans la prise en charge des patients ou des usagers.</t>
+    <t>Rôle du professionnel dans la prise en charge des patients ou des usagers (Synonyme : role).</t>
   </si>
   <si>
     <t>Liste des rôles</t>
@@ -1226,10 +1187,7 @@
     <t>metierPharmacienR06</t>
   </si>
   <si>
-    <t>Section du tableau de l’Ordre des pharmaciens (CNOP).</t>
-  </si>
-  <si>
-    <t>Synonyme : sectionOrdrePharmacien</t>
+    <t>Section du tableau de l’Ordre des pharmaciens (CNOP) (Synonyme : sectionOrdrePharmacien).</t>
   </si>
   <si>
     <t>Liste des sections du tableau CNOP</t>
@@ -1244,10 +1202,7 @@
     <t>metierPharmacienG05</t>
   </si>
   <si>
-    <t>Sous-section ou à défaut section du tableau de l’Ordre des pharmaciens (CNOP).</t>
-  </si>
-  <si>
-    <t>Synonyme : sousSectionOrdrePharmacien</t>
+    <t>Sous-section ou à défaut section du tableau de l’Ordre des pharmaciens (CNOP). (Synonyme : sousSectionOrdrePharmacien)</t>
   </si>
   <si>
     <t>Liste des sous-sections du tableau CNOP</t>
@@ -1306,10 +1261,7 @@
     <t>attributionParticuliere</t>
   </si>
   <si>
-    <t>Activité ponctuelle du professionnel de type expertise.</t>
-  </si>
-  <si>
-    <t>Synonyme : attributionParticuliere</t>
+    <t>Activité ponctuelle du professionnel de type expertise (Synonyme : attributionParticuliere).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J90-AttributionParticuliere-RASS/FHIR/JDV-J90-AttributionParticuliere-RASS</t>
@@ -1321,10 +1273,7 @@
     <t>savoirFaireR38</t>
   </si>
   <si>
-    <t>Spécialité ordinale  reconnue par une autorité d'enregistrement (Ordre ou SSA).</t>
-  </si>
-  <si>
-    <t>Synonyme : specialite</t>
+    <t>Spécialité ordinale  reconnue par une autorité d'enregistrement (Ordre ou SSA) (Synonyme : specialite).</t>
   </si>
   <si>
     <t>Liste des spécialités ordinales</t>
@@ -1339,10 +1288,7 @@
     <t>savoirFaireR39</t>
   </si>
   <si>
-    <t>Compétence acquise par le professionnel.</t>
-  </si>
-  <si>
-    <t>Synonyme : competence</t>
+    <t>Compétence acquise par le professionnel (Synonyme : competence).</t>
   </si>
   <si>
     <t>Liste des compétences</t>
@@ -1354,10 +1300,7 @@
     <t>savoirFaireR40</t>
   </si>
   <si>
-    <t>Compétence exclusive exercée par le professionnel à titre exclusif.</t>
-  </si>
-  <si>
-    <t>Synonyme : competenceExclusive</t>
+    <t>Compétence exclusive exercée par le professionnel à titre exclusif (Synonyme : competenceExclusive).</t>
   </si>
   <si>
     <t>Liste des compétences exclusives</t>
@@ -1369,10 +1312,7 @@
     <t>savoirFaireR42</t>
   </si>
   <si>
-    <t>Diplôme d'études spécialisées complémentaires (DESC).</t>
-  </si>
-  <si>
-    <t>Synonyme : DESCnonQualifian</t>
+    <t>Diplôme d'études spécialisées complémentaires (DESC). Synonyme : DESCnonQualifian</t>
   </si>
   <si>
     <t>Liste des DESC</t>
@@ -1384,10 +1324,7 @@
     <t>savoirFaireR43</t>
   </si>
   <si>
-    <t>Capacité (savoir-faire)d e médecine</t>
-  </si>
-  <si>
-    <t>Synonyme : capaciteSavoirFaire</t>
+    <t>Capacité (savoir-faire)de médecine (Synonyme : capaciteSavoirFaire)</t>
   </si>
   <si>
     <t>Liste des capacités</t>
@@ -1399,10 +1336,7 @@
     <t>savoirFaireR44</t>
   </si>
   <si>
-    <t>Qualification de praticien adjoint contractuel.</t>
-  </si>
-  <si>
-    <t>Synonyme : qualificationPAC</t>
+    <t>Qualification de praticien adjoint contractuel (Synonyme : qualificationPAC).</t>
   </si>
   <si>
     <t>Liste des qualifications</t>
@@ -1414,10 +1348,7 @@
     <t>savoirFaireR45</t>
   </si>
   <si>
-    <t>Fonction qualifiée.</t>
-  </si>
-  <si>
-    <t>Synonyme : fonctionQualifiee</t>
+    <t>Fonction qualifiée (Synonyme : fonctionQualifiee).</t>
   </si>
   <si>
     <t>Liste des fonctions qualifiées</t>
@@ -1429,10 +1360,7 @@
     <t>savoirFaireR97</t>
   </si>
   <si>
-    <t>Droit d'exercice complémentaire.</t>
-  </si>
-  <si>
-    <t>Synonyme : droitExerciceComplementaire</t>
+    <t>Droit d'exercice complémentaire (Synonyme : droitExerciceComplementaire).</t>
   </si>
   <si>
     <t>Liste des droits d'exercice complémentaires</t>
@@ -1444,10 +1372,7 @@
     <t>savoirFaireG13</t>
   </si>
   <si>
-    <t>Orientation particulière.</t>
-  </si>
-  <si>
-    <t>Synonyme : orientationParticuliere</t>
+    <t>Orientation particulière (Synonyme : orientationParticuliere).</t>
   </si>
   <si>
     <t>Liste des orientations particulières</t>
@@ -1459,10 +1384,7 @@
     <t>typeSavoirFaire</t>
   </si>
   <si>
-    <t>Le type de savoir-faire (qualifications/autres attributions).</t>
-  </si>
-  <si>
-    <t>Synonyme : typeSavoirFaire</t>
+    <t>Le type de savoir-faire (qualifications/autres attributions). (Synonyme : typeSavoirFaire)</t>
   </si>
   <si>
     <t>Liste des types de savoir-faire</t>
@@ -1478,13 +1400,10 @@
 </t>
   </si>
   <si>
-    <t>Référence vers la location dans PractitionerRole.contained représentant les coordonnées de l'activité.</t>
+    <t>Référence vers la location dans PractitionerRole.contained représentant les coordonnées de l'activité (idLocation).</t>
   </si>
   <si>
     <t>The location(s) at which this practitioner provides care.</t>
-  </si>
-  <si>
-    <t>idLocation</t>
   </si>
   <si>
     <t>PractitionerRole.healthcareService</t>
@@ -1500,9 +1419,6 @@
     <t>The list of healthcare services that this worker provides for this role's Organization/Location(s).</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
@@ -1537,10 +1453,7 @@
 </t>
   </si>
   <si>
-    <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice.</t>
-  </si>
-  <si>
-    <t>Synonyme : BoiteLettreMSS</t>
+    <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice (Synonyme : BoiteLettreMSS).</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -4946,11 +4859,9 @@
       <c r="M29" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>35</v>
@@ -5016,10 +4927,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5116,10 +5027,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5218,10 +5129,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5247,16 +5158,16 @@
         <v>123</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>35</v>
@@ -5281,31 +5192,31 @@
         <v>35</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AA32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -5322,10 +5233,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5348,19 +5259,19 @@
         <v>43</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>35</v>
@@ -5388,28 +5299,28 @@
         <v>105</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -5426,10 +5337,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5455,16 +5366,16 @@
         <v>89</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>35</v>
@@ -5477,43 +5388,43 @@
         <v>35</v>
       </c>
       <c r="T34" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5530,10 +5441,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5559,13 +5470,13 @@
         <v>56</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5579,43 +5490,43 @@
         <v>35</v>
       </c>
       <c r="T35" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5632,10 +5543,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5658,16 +5569,16 @@
         <v>43</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5717,7 +5628,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5729,15 +5640,15 @@
         <v>54</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5760,16 +5671,16 @@
         <v>43</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5819,7 +5730,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -5831,15 +5742,15 @@
         <v>54</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5862,26 +5773,26 @@
         <v>43</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="O38" t="s" s="2">
+      <c r="P38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q38" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="P38" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q38" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="R38" t="s" s="2">
         <v>35</v>
       </c>
@@ -5925,7 +5836,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -5942,10 +5853,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5968,19 +5879,19 @@
         <v>43</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>35</v>
@@ -6029,7 +5940,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -6041,15 +5952,15 @@
         <v>54</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6146,10 +6057,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6248,10 +6159,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6274,16 +6185,16 @@
         <v>43</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6333,7 +6244,7 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6342,7 +6253,7 @@
         <v>42</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>81</v>
@@ -6350,10 +6261,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6376,68 +6287,68 @@
         <v>43</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="R43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6446,7 +6357,7 @@
         <v>42</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>81</v>
@@ -6454,10 +6365,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6480,16 +6391,16 @@
         <v>43</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6539,7 +6450,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6551,15 +6462,15 @@
         <v>54</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6582,16 +6493,16 @@
         <v>43</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6641,7 +6552,7 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -6653,15 +6564,15 @@
         <v>54</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6684,19 +6595,19 @@
         <v>43</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>35</v>
@@ -6721,13 +6632,13 @@
         <v>35</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>35</v>
@@ -6745,7 +6656,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -6762,10 +6673,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6862,10 +6773,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6964,10 +6875,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6993,16 +6904,16 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>35</v>
@@ -7039,7 +6950,7 @@
         <v>35</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -7049,7 +6960,7 @@
         <v>68</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7066,13 +6977,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>35</v>
@@ -7097,16 +7008,16 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>35</v>
@@ -7131,13 +7042,13 @@
         <v>35</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>35</v>
@@ -7155,7 +7066,7 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7172,13 +7083,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>35</v>
@@ -7203,16 +7114,16 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>35</v>
@@ -7237,13 +7148,13 @@
         <v>35</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>35</v>
@@ -7261,7 +7172,7 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -7278,13 +7189,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>35</v>
@@ -7309,16 +7220,16 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>35</v>
@@ -7343,13 +7254,13 @@
         <v>35</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>35</v>
@@ -7367,7 +7278,7 @@
         <v>35</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7384,13 +7295,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>35</v>
@@ -7415,16 +7326,16 @@
         <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>35</v>
@@ -7449,13 +7360,13 @@
         <v>35</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>35</v>
@@ -7473,7 +7384,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7490,13 +7401,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>35</v>
@@ -7521,16 +7432,16 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7555,13 +7466,13 @@
         <v>35</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>35</v>
@@ -7579,7 +7490,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -7596,13 +7507,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>35</v>
@@ -7627,16 +7538,16 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -7661,13 +7572,13 @@
         <v>35</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>35</v>
@@ -7685,7 +7596,7 @@
         <v>35</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -7702,13 +7613,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>35</v>
@@ -7733,16 +7644,16 @@
         <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -7767,13 +7678,13 @@
         <v>35</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>35</v>
@@ -7791,7 +7702,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -7808,13 +7719,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>35</v>
@@ -7839,16 +7750,16 @@
         <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O57" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>35</v>
@@ -7873,13 +7784,13 @@
         <v>35</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>35</v>
@@ -7897,7 +7808,7 @@
         <v>35</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
@@ -7914,13 +7825,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>35</v>
@@ -7945,16 +7856,16 @@
         <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O58" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>35</v>
@@ -7979,13 +7890,13 @@
         <v>35</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>35</v>
@@ -8003,7 +7914,7 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -8020,13 +7931,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>35</v>
@@ -8051,16 +7962,16 @@
         <v>101</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>35</v>
@@ -8085,13 +7996,13 @@
         <v>35</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>35</v>
@@ -8109,7 +8020,7 @@
         <v>35</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
@@ -8126,13 +8037,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>35</v>
@@ -8157,16 +8068,16 @@
         <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>35</v>
@@ -8191,13 +8102,13 @@
         <v>35</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>35</v>
@@ -8215,7 +8126,7 @@
         <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
@@ -8232,13 +8143,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>35</v>
@@ -8263,16 +8174,16 @@
         <v>101</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>35</v>
@@ -8297,13 +8208,13 @@
         <v>35</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>35</v>
@@ -8321,7 +8232,7 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -8338,13 +8249,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>35</v>
@@ -8369,16 +8280,16 @@
         <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>35</v>
@@ -8403,13 +8314,13 @@
         <v>35</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>35</v>
@@ -8427,7 +8338,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8444,13 +8355,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>35</v>
@@ -8475,16 +8386,16 @@
         <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="M63" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>35</v>
@@ -8509,13 +8420,13 @@
         <v>35</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>35</v>
@@ -8533,7 +8444,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -8550,13 +8461,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>35</v>
@@ -8581,16 +8492,16 @@
         <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="M64" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>35</v>
@@ -8615,13 +8526,13 @@
         <v>35</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>35</v>
@@ -8639,7 +8550,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -8656,10 +8567,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8685,16 +8596,16 @@
         <v>56</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>35</v>
@@ -8743,7 +8654,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -8760,10 +8671,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8786,16 +8697,16 @@
         <v>43</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8821,22 +8732,22 @@
         <v>35</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>35</v>
@@ -8845,7 +8756,7 @@
         <v>68</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -8862,13 +8773,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>35</v>
@@ -8890,16 +8801,16 @@
         <v>43</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8925,11 +8836,11 @@
         <v>35</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>35</v>
@@ -8947,7 +8858,7 @@
         <v>35</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -8964,13 +8875,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>35</v>
@@ -8992,16 +8903,16 @@
         <v>43</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9027,13 +8938,13 @@
         <v>35</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>35</v>
@@ -9051,7 +8962,7 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
@@ -9068,13 +8979,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>35</v>
@@ -9096,16 +9007,16 @@
         <v>43</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9131,13 +9042,13 @@
         <v>35</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>35</v>
@@ -9155,7 +9066,7 @@
         <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -9172,13 +9083,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>35</v>
@@ -9200,16 +9111,16 @@
         <v>43</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9235,13 +9146,13 @@
         <v>35</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>35</v>
@@ -9259,7 +9170,7 @@
         <v>35</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -9276,13 +9187,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>35</v>
@@ -9304,16 +9215,16 @@
         <v>43</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9339,13 +9250,13 @@
         <v>35</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>35</v>
@@ -9363,7 +9274,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -9380,13 +9291,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>35</v>
@@ -9408,16 +9319,16 @@
         <v>43</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>440</v>
+        <v>391</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9443,13 +9354,13 @@
         <v>35</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>35</v>
@@ -9467,7 +9378,7 @@
         <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -9484,13 +9395,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>35</v>
@@ -9512,16 +9423,16 @@
         <v>43</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9547,13 +9458,13 @@
         <v>35</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>35</v>
@@ -9571,7 +9482,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -9588,13 +9499,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>35</v>
@@ -9616,16 +9527,16 @@
         <v>43</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9651,13 +9562,13 @@
         <v>35</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>35</v>
@@ -9675,7 +9586,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -9692,13 +9603,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>35</v>
@@ -9720,16 +9631,16 @@
         <v>43</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>455</v>
+        <v>391</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9755,13 +9666,13 @@
         <v>35</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>35</v>
@@ -9779,7 +9690,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -9796,13 +9707,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>35</v>
@@ -9824,16 +9735,16 @@
         <v>43</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>460</v>
+        <v>391</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9859,13 +9770,13 @@
         <v>35</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>35</v>
@@ -9883,7 +9794,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -9900,13 +9811,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>35</v>
@@ -9928,16 +9839,16 @@
         <v>43</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>465</v>
+        <v>391</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9963,13 +9874,13 @@
         <v>35</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>35</v>
@@ -9987,7 +9898,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -10004,10 +9915,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10030,16 +9941,16 @@
         <v>43</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>472</v>
+        <v>292</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10089,7 +10000,7 @@
         <v>35</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -10101,15 +10012,15 @@
         <v>54</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10132,16 +10043,16 @@
         <v>35</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>477</v>
+        <v>292</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10191,7 +10102,7 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -10203,15 +10114,15 @@
         <v>54</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10234,17 +10145,17 @@
         <v>43</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>35</v>
@@ -10281,7 +10192,7 @@
         <v>35</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
@@ -10291,7 +10202,7 @@
         <v>68</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -10303,18 +10214,18 @@
         <v>54</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>484</v>
+        <v>456</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>486</v>
+        <v>458</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>35</v>
@@ -10336,19 +10247,17 @@
         <v>35</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>35</v>
@@ -10397,7 +10306,7 @@
         <v>35</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -10409,15 +10318,15 @@
         <v>54</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>484</v>
+        <v>456</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10440,16 +10349,16 @@
         <v>35</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -10499,7 +10408,7 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -10516,10 +10425,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10616,10 +10525,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>496</v>
+        <v>467</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>496</v>
+        <v>467</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10718,14 +10627,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>497</v>
+        <v>468</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>497</v>
+        <v>468</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>498</v>
+        <v>469</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -10747,10 +10656,10 @@
         <v>62</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>65</v>
@@ -10805,7 +10714,7 @@
         <v>35</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>501</v>
+        <v>472</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>36</v>
@@ -10822,10 +10731,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10851,13 +10760,13 @@
         <v>123</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>503</v>
+        <v>474</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>475</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>505</v>
+        <v>476</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10883,13 +10792,13 @@
         <v>35</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>35</v>
@@ -10907,7 +10816,7 @@
         <v>35</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>36</v>
@@ -10924,10 +10833,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10950,13 +10859,13 @@
         <v>35</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11007,7 +10916,7 @@
         <v>35</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>36</v>
@@ -11024,10 +10933,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11050,16 +10959,16 @@
         <v>35</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11109,7 +11018,7 @@
         <v>35</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
@@ -11126,10 +11035,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11152,16 +11061,16 @@
         <v>35</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11211,7 +11120,7 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -11228,10 +11137,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11254,13 +11163,13 @@
         <v>35</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L90" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="M90" t="s" s="2">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11311,7 +11220,7 @@
         <v>35</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
@@ -11328,10 +11237,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11428,10 +11337,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11530,14 +11439,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>498</v>
+        <v>469</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -11559,10 +11468,10 @@
         <v>62</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>65</v>
@@ -11617,7 +11526,7 @@
         <v>35</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>501</v>
+        <v>472</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -11634,10 +11543,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11663,13 +11572,13 @@
         <v>56</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>505</v>
+        <v>476</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11719,7 +11628,7 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>42</v>
@@ -11736,10 +11645,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11762,16 +11671,16 @@
         <v>35</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11821,7 +11730,7 @@
         <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -11833,15 +11742,15 @@
         <v>54</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11867,13 +11776,13 @@
         <v>56</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>505</v>
+        <v>476</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11923,7 +11832,7 @@
         <v>35</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>36</v>
@@ -11940,10 +11849,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11966,19 +11875,19 @@
         <v>35</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>477</v>
+        <v>292</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>35</v>
@@ -12027,7 +11936,7 @@
         <v>35</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
@@ -12039,7 +11948,7 @@
         <v>54</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:51:06+00:00</t>
+    <t>2023-07-11T12:08:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/main/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
